--- a/topics/projects/Presentations.xlsx
+++ b/topics/projects/Presentations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/Studies/International Business Management (B. A.)/Data Science and Data Analytics/Projects/Data-Science-and-Data-Analytics/topics/projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56234828-DE88-FB4F-8B68-8C169B9062F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0947A406-ACA7-3D4B-87EB-2791F6AD1504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="16940" xr2:uid="{523D878C-183F-FF45-8FEA-63E7989E711F}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="16860" xr2:uid="{523D878C-183F-FF45-8FEA-63E7989E711F}"/>
   </bookViews>
   <sheets>
     <sheet name="Presentations" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
   <si>
     <t>Leonie</t>
   </si>
@@ -180,6 +180,57 @@
   </si>
   <si>
     <t>3-4</t>
+  </si>
+  <si>
+    <t>Dominic</t>
+  </si>
+  <si>
+    <t>Kaggle</t>
+  </si>
+  <si>
+    <t>Age variation assumption, what predicts market vaule</t>
+  </si>
+  <si>
+    <t>3D plot, why are the dots not smaller in the background?</t>
+  </si>
+  <si>
+    <t>Did you filter goal keepers out?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mira </t>
+  </si>
+  <si>
+    <t>Esra</t>
+  </si>
+  <si>
+    <t>Kaggle &amp; Yahoo</t>
+  </si>
+  <si>
+    <t>öfters umgangssprachlich</t>
+  </si>
+  <si>
+    <t>Link only?</t>
+  </si>
+  <si>
+    <t>gute Ausdrucksweise</t>
+  </si>
+  <si>
+    <t>Stella</t>
+  </si>
+  <si>
+    <t>Athina</t>
+  </si>
+  <si>
+    <t>How was a single video identifyable?</t>
+  </si>
+  <si>
+    <t>good idea with creating a own rate</t>
+  </si>
+  <si>
+    <t>Github</t>
+  </si>
+  <si>
+    <t>Github + quarto</t>
   </si>
 </sst>
 </file>
@@ -1023,21 +1074,33 @@
       <c r="I8" s="9"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="12"/>
+      <c r="L8" s="1"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="I9" s="9"/>
       <c r="J9" s="1"/>
       <c r="K9" s="17"/>
-      <c r="L9" s="12"/>
+      <c r="L9" s="12" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
@@ -1046,7 +1109,9 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="H10" s="1"/>
       <c r="I10" s="9"/>
       <c r="J10" s="1"/>
@@ -1054,22 +1119,36 @@
       <c r="L10" s="12"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="E11" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="9"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="12"/>
+      <c r="K11" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1078,8 +1157,12 @@
       <c r="H12" s="1"/>
       <c r="I12" s="9"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="12"/>
+      <c r="K12" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
@@ -1096,22 +1179,36 @@
       <c r="L13" s="12"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="E14" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="9"/>
       <c r="J14" s="1"/>
       <c r="K14" s="17"/>
-      <c r="L14" s="12"/>
+      <c r="L14" s="12" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -1121,7 +1218,9 @@
       <c r="I15" s="9"/>
       <c r="J15" s="1"/>
       <c r="K15" s="17"/>
-      <c r="L15" s="12"/>
+      <c r="L15" s="12" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
@@ -1134,8 +1233,8 @@
       <c r="H16" s="1"/>
       <c r="I16" s="9"/>
       <c r="J16" s="1"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="12"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>

--- a/topics/projects/Presentations.xlsx
+++ b/topics/projects/Presentations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/Studies/International Business Management (B. A.)/Data Science and Data Analytics/Projects/Data-Science-and-Data-Analytics/topics/projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0947A406-ACA7-3D4B-87EB-2791F6AD1504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AA8786-CAC5-5143-94C8-4604D46806F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="16860" xr2:uid="{523D878C-183F-FF45-8FEA-63E7989E711F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
   <si>
     <t>Leonie</t>
   </si>
@@ -231,6 +231,45 @@
   </si>
   <si>
     <t>Github + quarto</t>
+  </si>
+  <si>
+    <t>Laurine</t>
+  </si>
+  <si>
+    <t>Eric</t>
+  </si>
+  <si>
+    <t>Mats</t>
+  </si>
+  <si>
+    <t>reading from cards</t>
+  </si>
+  <si>
+    <t>fine, performance, english a bit unsteady</t>
+  </si>
+  <si>
+    <t>description of the data transformation</t>
+  </si>
+  <si>
+    <t>data viz</t>
+  </si>
+  <si>
+    <t>How did you add missing values?</t>
+  </si>
+  <si>
+    <t>why accumulated figures? What did you do with it after?</t>
+  </si>
+  <si>
+    <t>Quarto presentation</t>
+  </si>
+  <si>
+    <t>Hosna</t>
+  </si>
+  <si>
+    <t>How are the datasets connected?</t>
+  </si>
+  <si>
+    <t>reading from cards, monotonic reading</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1037,9 @@
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
@@ -1237,8 +1278,12 @@
       <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -1248,25 +1293,40 @@
       <c r="I17" s="9"/>
       <c r="J17" s="1"/>
       <c r="K17" s="17"/>
-      <c r="L17" s="12"/>
+      <c r="L17" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="1"/>
+      <c r="J18" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="K18" s="17"/>
-      <c r="L18" s="12"/>
+      <c r="L18" s="12" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="A19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -1274,9 +1334,13 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="K19" s="17"/>
-      <c r="L19" s="12"/>
+      <c r="L19" s="12" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
@@ -1290,11 +1354,17 @@
       <c r="I20" s="9"/>
       <c r="J20" s="1"/>
       <c r="K20" s="17"/>
-      <c r="L20" s="12"/>
+      <c r="L20" s="12" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -1302,7 +1372,9 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K21" s="17"/>
       <c r="L21" s="12"/>
     </row>

--- a/topics/projects/Presentations.xlsx
+++ b/topics/projects/Presentations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/Studies/International Business Management (B. A.)/Data Science and Data Analytics/Projects/Data-Science-and-Data-Analytics/topics/projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AA8786-CAC5-5143-94C8-4604D46806F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D12BB1-81FA-BE45-9CE6-1FB5436E31F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="16860" xr2:uid="{523D878C-183F-FF45-8FEA-63E7989E711F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="73">
   <si>
     <t>Leonie</t>
   </si>
@@ -131,9 +131,6 @@
     <t>add Spotify API audio features that where discontinued</t>
   </si>
   <si>
-    <t>Is the scope realistic?</t>
-  </si>
-  <si>
     <t>Do they show that they understand its structure?</t>
   </si>
   <si>
@@ -146,12 +143,6 @@
     <t>Grade</t>
   </si>
   <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>Questions</t>
   </si>
   <si>
@@ -179,9 +170,6 @@
     <t>Have you asked AI how to handle the dataset?</t>
   </si>
   <si>
-    <t>3-4</t>
-  </si>
-  <si>
     <t>Dominic</t>
   </si>
   <si>
@@ -270,6 +258,24 @@
   </si>
   <si>
     <t>reading from cards, monotonic reading</t>
+  </si>
+  <si>
+    <t>1,7</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>2,7</t>
+  </si>
+  <si>
+    <t>3,7</t>
   </si>
 </sst>
 </file>
@@ -901,47 +907,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E16F357A-B2B9-7D4B-A294-58C0E959DBB6}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="56.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="90.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="53.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="53.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="47.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="76.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="49" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="49.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="90.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="47.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="76.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="49" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="49.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="4" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" s="16" t="s">
+      <c r="G1" s="5"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="7" t="s">
         <v>4</v>
@@ -950,32 +954,26 @@
         <v>5</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>7</v>
-      </c>
       <c r="F2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="18"/>
-      <c r="K2" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" s="11" t="s">
+      <c r="I2" s="18"/>
+      <c r="J2" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -985,25 +983,24 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="1" t="s">
+      <c r="H3" s="15"/>
+      <c r="I3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K3" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1011,57 +1008,57 @@
         <v>12</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="1" t="s">
+      <c r="H4" s="9"/>
+      <c r="I4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="12"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="9"/>
+      <c r="I5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1069,41 +1066,39 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="12"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I6" s="1"/>
+      <c r="J6" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" s="12"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="17"/>
-      <c r="L7" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" s="9"/>
+      <c r="I7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="17"/>
+      <c r="K7" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1111,101 +1106,96 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="9"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="12"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="1"/>
-      <c r="K11" t="s">
-        <v>51</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="9"/>
+      <c r="I11" s="1"/>
+      <c r="J11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" s="9"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1213,57 +1203,54 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="12"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" s="9"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" s="9"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1271,78 +1258,74 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H17" s="9"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J18" s="17"/>
+      <c r="K18" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="K18" s="17"/>
-      <c r="L18" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K19" s="17"/>
-      <c r="L19" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H19" s="9"/>
+      <c r="I19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J19" s="17"/>
+      <c r="K19" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1350,35 +1333,33 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H20" s="9"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="12"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K21" s="17"/>
-      <c r="L21" s="12"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H21" s="9"/>
+      <c r="I21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J21" s="17"/>
+      <c r="K21" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1386,13 +1367,12 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="12"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H22" s="9"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="12"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1400,11 +1380,10 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="12"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
